--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:19</t>
+    <t xml:space="preserve">2026-09-09 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:15</t>
+    <t xml:space="preserve">2026-09-17 14:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
@@ -162,12 +162,12 @@
     <t xml:space="preserve">Lo Prado</t>
   </si>
   <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Ramón</t>
   </si>
   <si>
-    <t xml:space="preserve">Independencia</t>
-  </si>
-  <si>
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:10</t>
+    <t xml:space="preserve">2026-09-23 12:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1345,7 +1345,7 @@
         <v>48</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>13131</v>
+        <v>13108</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>2018</v>
@@ -1362,7 +1362,7 @@
         <v>49</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>13108</v>
+        <v>13131</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>2018</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:39</t>
+    <t xml:space="preserve">2026-10-02 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2018_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:41</t>
+    <t xml:space="preserve">2026-10-05 11:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
